--- a/docs/data/jp/xlsx/3911.xlsx
+++ b/docs/data/jp/xlsx/3911.xlsx
@@ -6412,7 +6412,7 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>Distribution Profit NOI</t>
+          <t>수취 분배금</t>
         </is>
       </c>
       <c r="D90" s="22" t="n">
@@ -8450,7 +8450,7 @@
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>Amortization Of Contents Ope CF</t>
+          <t>콘텐츠 상각비</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
@@ -8496,7 +8496,7 @@
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss On Arrangement Of Subsidiaries And Affiliates Ope CF</t>
+          <t>관계회사 청산손실 충당금 증감(△ 감소)</t>
         </is>
       </c>
       <c r="P131" s="22" t="n">
@@ -8694,7 +8694,7 @@
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>Distribusion Profit Ope CF</t>
+          <t>수취 분배금</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
@@ -13243,7 +13243,7 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>Contents CA</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="D78" s="22" t="n">
